--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\qt\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55C4389-5D55-4F19-BCCD-9B548B1681AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -22,13 +28,13 @@
     <t>Username</t>
   </si>
   <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Full Name</t>
-  </si>
-  <si>
-    <t>Phone</t>
+    <t xml:space="preserve">Password </t>
+  </si>
+  <si>
+    <t>Fullname</t>
+  </si>
+  <si>
+    <t>PhoneNumber</t>
   </si>
   <si>
     <t>Address</t>
@@ -37,10 +43,10 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Birthday</t>
-  </si>
-  <si>
-    <t>Created_At</t>
+    <t>DateOfBirth</t>
+  </si>
+  <si>
+    <t>Create_At</t>
   </si>
   <si>
     <t>Update_At</t>
@@ -49,24 +55,72 @@
     <t>Balance</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>IsAdmin</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Role</t>
+    <t>Transaction_Status</t>
+  </si>
+  <si>
+    <t>is_admin</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>role</t>
   </si>
   <si>
     <t>test1</t>
   </si>
   <si>
+    <t>19/10/1997</t>
+  </si>
+  <si>
+    <t>2025-03-24 18:42:54</t>
+  </si>
+  <si>
+    <t>2025-03-24 21:00:35</t>
+  </si>
+  <si>
+    <t>nhận tiền</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
     <t>test2</t>
   </si>
   <si>
+    <t>10:31 23/03/2025</t>
+  </si>
+  <si>
+    <t>2025-03-25 21:37:57</t>
+  </si>
+  <si>
+    <t>chuyển điểm</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>le hoa</t>
+  </si>
+  <si>
+    <t>0123654</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>00000000000</t>
+  </si>
+  <si>
+    <t>co nguyet</t>
+  </si>
+  <si>
     <t>test3</t>
   </si>
   <si>
@@ -76,91 +130,48 @@
     <t>test5</t>
   </si>
   <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Admin Test</t>
-  </si>
-  <si>
-    <t>User Two</t>
-  </si>
-  <si>
-    <t>User Three</t>
-  </si>
-  <si>
-    <t>User Four</t>
-  </si>
-  <si>
-    <t>User Five</t>
-  </si>
-  <si>
-    <t>0123456789</t>
-  </si>
-  <si>
-    <t>Address 1</t>
-  </si>
-  <si>
-    <t>Address 2</t>
-  </si>
-  <si>
-    <t>Address 3</t>
-  </si>
-  <si>
-    <t>Address 4</t>
-  </si>
-  <si>
-    <t>Address 5</t>
-  </si>
-  <si>
-    <t>test1@example.com</t>
-  </si>
-  <si>
-    <t>test2@example.com</t>
-  </si>
-  <si>
-    <t>test3@example.com</t>
-  </si>
-  <si>
-    <t>test4@example.com</t>
-  </si>
-  <si>
-    <t>test5@example.com</t>
-  </si>
-  <si>
-    <t>1990-01-01</t>
-  </si>
-  <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>user</t>
+    <t>l@</t>
+  </si>
+  <si>
+    <t>le thanh nguye</t>
+  </si>
+  <si>
+    <t>033857590</t>
+  </si>
+  <si>
+    <t>1 hoang cau</t>
+  </si>
+  <si>
+    <t>Chuyển tiền thành công</t>
+  </si>
+  <si>
+    <t>Nhận tiền</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -180,28 +191,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -209,6 +236,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -223,28 +258,28 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="0000FF"/>
@@ -287,6 +322,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -321,6 +357,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -344,7 +381,6 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
@@ -355,31 +391,31 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -401,7 +437,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -459,7 +495,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -472,13 +508,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -496,45 +531,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:O6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.69921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="18.8984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.09765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15" style="5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -543,228 +595,243 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H3" s="6">
+        <v>35722</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1">
+        <v>22394</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="14.4">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2">
-        <v>10000</v>
-      </c>
-      <c r="M2">
+      <c r="E4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="1">
+        <v>2396</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
         <v>1</v>
       </c>
-      <c r="N2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" t="s">
-        <v>40</v>
+      <c r="O4" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="5" spans="1:15" ht="14.4">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="I5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
+      <c r="J5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="1">
+        <v>2395</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="14.4">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3">
-        <v>5000</v>
-      </c>
-      <c r="M3">
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="1">
+        <v>2395</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="1">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4">
-        <v>3000</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5">
-        <v>2000</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6">
-        <v>1000</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-      <c r="O6" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\qt\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\wallet_app\moenywallet\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55C4389-5D55-4F19-BCCD-9B548B1681AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA38817-C991-466D-BD9D-6FE49D60D287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>ID</t>
   </si>
@@ -55,108 +55,125 @@
     <t>Balance</t>
   </si>
   <si>
+    <t>is_admin</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>19/10/1997</t>
+  </si>
+  <si>
+    <t>2025-03-24 21:00:35</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>test2</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>test3</t>
+  </si>
+  <si>
+    <t>test4</t>
+  </si>
+  <si>
+    <t>test5</t>
+  </si>
+  <si>
+    <t>1 hoang cau</t>
+  </si>
+  <si>
+    <t>test6</t>
+  </si>
+  <si>
+    <t>8d969eef6ecad3c29a3a629280e686cf0c3f5d5a86aff3ca12020c923adc6c92</t>
+  </si>
+  <si>
+    <t>01/01/2000</t>
+  </si>
+  <si>
+    <t>test7</t>
+  </si>
+  <si>
+    <t>test8</t>
+  </si>
+  <si>
+    <t>test9</t>
+  </si>
+  <si>
+    <t>test10</t>
+  </si>
+  <si>
+    <t>le nguyen</t>
+  </si>
+  <si>
+    <t>Nhận điểm</t>
+  </si>
+  <si>
+    <t>test11</t>
+  </si>
+  <si>
+    <t>lenguyen@gmail.com</t>
+  </si>
+  <si>
     <t>Transaction_Status</t>
   </si>
   <si>
-    <t>is_admin</t>
-  </si>
-  <si>
-    <t>is_active</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>test1</t>
-  </si>
-  <si>
-    <t>19/10/1997</t>
-  </si>
-  <si>
-    <t>2025-03-24 18:42:54</t>
-  </si>
-  <si>
-    <t>2025-03-24 21:00:35</t>
-  </si>
-  <si>
-    <t>nhận tiền</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>test2</t>
-  </si>
-  <si>
-    <t>10:31 23/03/2025</t>
-  </si>
-  <si>
-    <t>2025-03-25 21:37:57</t>
-  </si>
-  <si>
-    <t>chuyển điểm</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>le hoa</t>
-  </si>
-  <si>
-    <t>0123654</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>00000000000</t>
-  </si>
-  <si>
-    <t>co nguyet</t>
-  </si>
-  <si>
-    <t>test3</t>
-  </si>
-  <si>
-    <t>test4</t>
-  </si>
-  <si>
-    <t>test5</t>
-  </si>
-  <si>
-    <t>l@</t>
-  </si>
-  <si>
-    <t>le thanh nguye</t>
-  </si>
-  <si>
-    <t>033857590</t>
-  </si>
-  <si>
-    <t>1 hoang cau</t>
-  </si>
-  <si>
-    <t>Chuyển tiền thành công</t>
-  </si>
-  <si>
-    <t>Nhận tiền</t>
+    <t>0987654321</t>
+  </si>
+  <si>
+    <t>2025-05-21 12:34:16</t>
+  </si>
+  <si>
+    <t>test12</t>
+  </si>
+  <si>
+    <t>test13</t>
+  </si>
+  <si>
+    <t>test14</t>
+  </si>
+  <si>
+    <t>test15</t>
+  </si>
+  <si>
+    <t>test16</t>
+  </si>
+  <si>
+    <t>nguyen1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>leme@gmail.com</t>
+  </si>
+  <si>
+    <t>2025-05-21 13:37:15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <numFmts>
+	</numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -167,11 +184,10 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -201,15 +217,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -219,15 +232,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -535,24 +539,27 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.69921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.8984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.09765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="15" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="19.5" customHeight="1">
+    <row r="1" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,254 +594,813 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="19.5" customHeight="1">
-      <c r="A2" s="8">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="I2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="1">
+        <v>95898</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="5">
+        <v>35722</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1602</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3">
+        <v>500</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="3">
+        <v>500</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="I7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="3">
+        <v>500</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="3">
+        <v>500</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="3">
+        <v>500</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="3">
+        <v>500</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="3">
+        <v>500</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="3">
+        <v>500</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="3">
+        <v>500</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3">
+        <v>500</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="3">
+        <v>500</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="3">
+        <v>500</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="3">
+        <v>500</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="1">
-        <v>1</v>
-      </c>
-      <c r="N2" s="1">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="19.5" customHeight="1">
-      <c r="A3" s="8">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="B18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="6">
-        <v>35722</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="1">
-        <v>22394</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="1">
-        <v>0</v>
-      </c>
-      <c r="N3" s="1">
-        <v>1</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="14.4">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="1">
-        <v>2396</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="14.4">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="1">
-        <v>2395</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="14.4">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="1">
-        <v>2395</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>25</v>
+      <c r="I18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="3">
+        <v>500</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>